--- a/backend/data/financials_by_company/11C.F.xlsx
+++ b/backend/data/financials_by_company/11C.F.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,618 +677,677 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-12832155.02</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="D2" t="n">
-        <v>91859276</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-67537658</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-67537658</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6889150</v>
-      </c>
-      <c r="H2" t="n">
-        <v>19813340</v>
-      </c>
-      <c r="I2" t="n">
-        <v>990906</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24321618</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3227343</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3676492</v>
-      </c>
-      <c r="M2" t="n">
-        <v>451476</v>
-      </c>
-      <c r="N2" t="n">
-        <v>877536</v>
-      </c>
-      <c r="O2" t="n">
-        <v>61594652.98</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6889150</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>76625854</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-2837672</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2417199</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2417199</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W2" t="n">
-        <v>6889150</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6889150</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6889150</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>6889150</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6889150</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-4123283</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2775867</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-66763185</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>48421309</v>
+        <v>-2072</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>69825</v>
       </c>
       <c r="AH2" t="n">
-        <v>18341876</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3676492</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-3250432</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>451476</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>877536</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>63919453</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>75634948</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>42319207</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>21094275</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18617529</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2476746</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1409489</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1262818</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>146671</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>139554401</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>990906</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>140545307</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>140545307</v>
-      </c>
+        <v>-69825</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1265091.44</v>
+        <v>323859.9267</v>
       </c>
       <c r="C3" t="n">
-        <v>0.19</v>
+        <v>0.1593</v>
       </c>
       <c r="D3" t="n">
-        <v>12772318</v>
+        <v>33488092</v>
       </c>
       <c r="E3" t="n">
-        <v>-6658376</v>
+        <v>2033019</v>
       </c>
       <c r="F3" t="n">
-        <v>-6658376</v>
+        <v>2033019</v>
       </c>
       <c r="G3" t="n">
-        <v>525609</v>
+        <v>22889816</v>
       </c>
       <c r="H3" t="n">
-        <v>4171765</v>
+        <v>5891465</v>
       </c>
       <c r="I3" t="n">
-        <v>802508</v>
+        <v>644158</v>
       </c>
       <c r="J3" t="n">
-        <v>6113942</v>
+        <v>35521111</v>
       </c>
       <c r="K3" t="n">
-        <v>326928</v>
+        <v>27713333</v>
       </c>
       <c r="L3" t="n">
-        <v>2191463</v>
+        <v>2151532</v>
       </c>
       <c r="M3" t="n">
-        <v>621519</v>
+        <v>486992</v>
       </c>
       <c r="N3" t="n">
-        <v>2786732</v>
+        <v>2638524</v>
       </c>
       <c r="O3" t="n">
-        <v>5918893.56</v>
+        <v>21180656.9267</v>
       </c>
       <c r="P3" t="n">
-        <v>525609</v>
+        <v>22889816</v>
       </c>
       <c r="Q3" t="n">
-        <v>44661592</v>
+        <v>54235293</v>
       </c>
       <c r="R3" t="n">
-        <v>7592337</v>
+        <v>19982658</v>
       </c>
       <c r="S3" t="n">
-        <v>2408935</v>
+        <v>2402635</v>
       </c>
       <c r="T3" t="n">
-        <v>2396407</v>
+        <v>2370153</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>9.66</v>
       </c>
       <c r="W3" t="n">
-        <v>525609</v>
+        <v>22889816</v>
       </c>
       <c r="X3" t="n">
-        <v>525609</v>
+        <v>22889816</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>525609</v>
+        <v>22889816</v>
       </c>
       <c r="AA3" t="n">
-        <v>525609</v>
+        <v>22889816</v>
       </c>
       <c r="AB3" t="n">
-        <v>525609</v>
+        <v>22889816</v>
       </c>
       <c r="AC3" t="n">
-        <v>-820200</v>
+        <v>4336525</v>
       </c>
       <c r="AD3" t="n">
-        <v>-294591</v>
+        <v>27226341</v>
       </c>
       <c r="AE3" t="n">
-        <v>-5552</v>
+        <v>12026</v>
       </c>
       <c r="AF3" t="n">
-        <v>18804</v>
+        <v>-12026</v>
       </c>
       <c r="AG3" t="n">
-        <v>-13252</v>
-      </c>
-      <c r="AH3" t="n">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>2191463</v>
+        <v>2151532</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-26250</v>
+        <v>25563</v>
       </c>
       <c r="AK3" t="n">
-        <v>621519</v>
+        <v>486992</v>
       </c>
       <c r="AL3" t="n">
-        <v>2786732</v>
+        <v>2638524</v>
       </c>
       <c r="AM3" t="n">
-        <v>7611140</v>
+        <v>19970634</v>
       </c>
       <c r="AN3" t="n">
-        <v>43859084</v>
+        <v>53591135</v>
       </c>
       <c r="AO3" t="n">
-        <v>28086396</v>
+        <v>31872847</v>
       </c>
       <c r="AP3" t="n">
-        <v>5787014</v>
+        <v>7807778</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2858174</v>
+        <v>5035631</v>
       </c>
       <c r="AR3" t="n">
-        <v>2928840</v>
+        <v>2772147</v>
       </c>
       <c r="AS3" t="n">
-        <v>993609</v>
+        <v>712985</v>
       </c>
       <c r="AT3" t="n">
-        <v>871413</v>
+        <v>624515</v>
       </c>
       <c r="AU3" t="n">
-        <v>122196</v>
+        <v>88470</v>
       </c>
       <c r="AV3" t="n">
-        <v>51470224</v>
+        <v>73561769</v>
       </c>
       <c r="AW3" t="n">
-        <v>802508</v>
+        <v>644158</v>
       </c>
       <c r="AX3" t="n">
-        <v>52272732</v>
+        <v>74205927</v>
       </c>
       <c r="AY3" t="n">
-        <v>52272732</v>
+        <v>74205927</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>323859.9267</v>
+        <v>-1265091.44</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1593</v>
+        <v>0.19</v>
       </c>
       <c r="D4" t="n">
-        <v>33488092</v>
+        <v>12772318</v>
       </c>
       <c r="E4" t="n">
-        <v>2033019</v>
+        <v>-6658376</v>
       </c>
       <c r="F4" t="n">
-        <v>2033019</v>
+        <v>-6658376</v>
       </c>
       <c r="G4" t="n">
-        <v>22889816</v>
+        <v>525609</v>
       </c>
       <c r="H4" t="n">
-        <v>5891465</v>
+        <v>4171765</v>
       </c>
       <c r="I4" t="n">
-        <v>644158</v>
+        <v>802508</v>
       </c>
       <c r="J4" t="n">
-        <v>35521111</v>
+        <v>6113942</v>
       </c>
       <c r="K4" t="n">
-        <v>27713333</v>
+        <v>326928</v>
       </c>
       <c r="L4" t="n">
-        <v>2151532</v>
+        <v>2191463</v>
       </c>
       <c r="M4" t="n">
-        <v>486992</v>
+        <v>621519</v>
       </c>
       <c r="N4" t="n">
-        <v>2638524</v>
+        <v>2786732</v>
       </c>
       <c r="O4" t="n">
-        <v>21180656.9267</v>
+        <v>5918893.56</v>
       </c>
       <c r="P4" t="n">
-        <v>22889816</v>
+        <v>525609</v>
       </c>
       <c r="Q4" t="n">
-        <v>54235293</v>
+        <v>44661592</v>
       </c>
       <c r="R4" t="n">
-        <v>19982658</v>
+        <v>7592337</v>
       </c>
       <c r="S4" t="n">
-        <v>2402635</v>
+        <v>2408935</v>
       </c>
       <c r="T4" t="n">
-        <v>2370153</v>
+        <v>2396407</v>
       </c>
       <c r="U4" t="n">
-        <v>9.529999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>9.66</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
-        <v>22889816</v>
+        <v>525609</v>
       </c>
       <c r="X4" t="n">
-        <v>22889816</v>
+        <v>525609</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>22889816</v>
+        <v>525609</v>
       </c>
       <c r="AA4" t="n">
-        <v>22889816</v>
+        <v>525609</v>
       </c>
       <c r="AB4" t="n">
-        <v>22889816</v>
+        <v>525609</v>
       </c>
       <c r="AC4" t="n">
-        <v>4336525</v>
+        <v>-820200</v>
       </c>
       <c r="AD4" t="n">
-        <v>27226341</v>
+        <v>-294591</v>
       </c>
       <c r="AE4" t="n">
-        <v>12026</v>
+        <v>-5552</v>
       </c>
       <c r="AF4" t="n">
-        <v>-12026</v>
+        <v>18804</v>
       </c>
       <c r="AG4" t="n">
+        <v>-13252</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>2151532</v>
+        <v>2191463</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25563</v>
+        <v>-26250</v>
       </c>
       <c r="AK4" t="n">
-        <v>486992</v>
+        <v>621519</v>
       </c>
       <c r="AL4" t="n">
-        <v>2638524</v>
+        <v>2786732</v>
       </c>
       <c r="AM4" t="n">
-        <v>19970634</v>
+        <v>7611140</v>
       </c>
       <c r="AN4" t="n">
-        <v>53591135</v>
+        <v>43859084</v>
       </c>
       <c r="AO4" t="n">
-        <v>31872847</v>
+        <v>28086396</v>
       </c>
       <c r="AP4" t="n">
-        <v>7807778</v>
+        <v>5787014</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5035631</v>
+        <v>2858174</v>
       </c>
       <c r="AR4" t="n">
-        <v>2772147</v>
+        <v>2928840</v>
       </c>
       <c r="AS4" t="n">
-        <v>712985</v>
+        <v>993609</v>
       </c>
       <c r="AT4" t="n">
-        <v>624515</v>
+        <v>871413</v>
       </c>
       <c r="AU4" t="n">
-        <v>88470</v>
+        <v>122196</v>
       </c>
       <c r="AV4" t="n">
-        <v>73561769</v>
+        <v>51470224</v>
       </c>
       <c r="AW4" t="n">
-        <v>644158</v>
+        <v>802508</v>
       </c>
       <c r="AX4" t="n">
-        <v>74205927</v>
+        <v>52272732</v>
       </c>
       <c r="AY4" t="n">
-        <v>74205927</v>
+        <v>52272732</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>96807.276</v>
+        <v>-12832155.02</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0989</v>
+        <v>0.19</v>
       </c>
       <c r="D5" t="n">
-        <v>41611314</v>
+        <v>91859276</v>
       </c>
       <c r="E5" t="n">
-        <v>978840</v>
+        <v>-67537658</v>
       </c>
       <c r="F5" t="n">
-        <v>978840</v>
+        <v>-67537658</v>
       </c>
       <c r="G5" t="n">
-        <v>28685582</v>
+        <v>6899150</v>
       </c>
       <c r="H5" t="n">
-        <v>8920103</v>
+        <v>19813340</v>
       </c>
       <c r="I5" t="n">
-        <v>534279</v>
+        <v>990906</v>
       </c>
       <c r="J5" t="n">
-        <v>42590154</v>
+        <v>24321618</v>
       </c>
       <c r="K5" t="n">
-        <v>31957858</v>
+        <v>3227343</v>
       </c>
       <c r="L5" t="n">
-        <v>-161810</v>
+        <v>3676492</v>
       </c>
       <c r="M5" t="n">
-        <v>123394</v>
+        <v>451476</v>
       </c>
       <c r="N5" t="n">
-        <v>190782</v>
+        <v>877536</v>
       </c>
       <c r="O5" t="n">
-        <v>27803549.276</v>
+        <v>61604652.98</v>
       </c>
       <c r="P5" t="n">
-        <v>28685582</v>
+        <v>6899150</v>
       </c>
       <c r="Q5" t="n">
-        <v>40021864</v>
+        <v>76625854</v>
       </c>
       <c r="R5" t="n">
-        <v>30031002</v>
+        <v>-2837672</v>
       </c>
       <c r="S5" t="n">
-        <v>2399332</v>
+        <v>2417199</v>
       </c>
       <c r="T5" t="n">
-        <v>2357095</v>
+        <v>2417199</v>
       </c>
       <c r="U5" t="n">
-        <v>11.96</v>
+        <v>2.85</v>
       </c>
       <c r="V5" t="n">
-        <v>12.17</v>
+        <v>2.85</v>
       </c>
       <c r="W5" t="n">
-        <v>28685582</v>
+        <v>6899150</v>
       </c>
       <c r="X5" t="n">
-        <v>28685582</v>
+        <v>6899150</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>28685582</v>
+        <v>6899150</v>
       </c>
       <c r="AA5" t="n">
-        <v>28685582</v>
+        <v>6899150</v>
       </c>
       <c r="AB5" t="n">
-        <v>28685582</v>
+        <v>6899150</v>
       </c>
       <c r="AC5" t="n">
-        <v>3148882</v>
+        <v>-4123283</v>
       </c>
       <c r="AD5" t="n">
-        <v>31834464</v>
+        <v>2775867</v>
       </c>
       <c r="AE5" t="n">
-        <v>-69825</v>
+        <v>-66763185</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2072</v>
+        <v>48421309</v>
       </c>
       <c r="AG5" t="n">
-        <v>69825</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-69825</v>
+        <v>18341876</v>
       </c>
       <c r="AI5" t="n">
-        <v>-161810</v>
+        <v>3676492</v>
       </c>
       <c r="AJ5" t="n">
-        <v>229198</v>
+        <v>-3250432</v>
       </c>
       <c r="AK5" t="n">
-        <v>123394</v>
+        <v>451476</v>
       </c>
       <c r="AL5" t="n">
-        <v>190782</v>
+        <v>877536</v>
       </c>
       <c r="AM5" t="n">
-        <v>30100827</v>
+        <v>63919453</v>
       </c>
       <c r="AN5" t="n">
-        <v>39487585</v>
+        <v>75634948</v>
       </c>
       <c r="AO5" t="n">
-        <v>19514763</v>
+        <v>42319207</v>
       </c>
       <c r="AP5" t="n">
-        <v>10632296</v>
+        <v>21094275</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8106242</v>
+        <v>18617529</v>
       </c>
       <c r="AR5" t="n">
-        <v>2526054</v>
+        <v>2476746</v>
       </c>
       <c r="AS5" t="n">
-        <v>19200848</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>1409489</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1262818</v>
+      </c>
       <c r="AU5" t="n">
-        <v>19200848</v>
+        <v>146671</v>
       </c>
       <c r="AV5" t="n">
-        <v>69588412</v>
+        <v>139554401</v>
       </c>
       <c r="AW5" t="n">
-        <v>534279</v>
+        <v>990906</v>
       </c>
       <c r="AX5" t="n">
-        <v>70122691</v>
+        <v>140545307</v>
       </c>
       <c r="AY5" t="n">
-        <v>70122691</v>
+        <v>140545307</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80531.27803099999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.396309</v>
+      </c>
+      <c r="D6" t="n">
+        <v>62731158</v>
+      </c>
+      <c r="E6" t="n">
+        <v>203203</v>
+      </c>
+      <c r="F6" t="n">
+        <v>203203</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50224225</v>
+      </c>
+      <c r="I6" t="n">
+        <v>793172</v>
+      </c>
+      <c r="J6" t="n">
+        <v>62934361</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11813015</v>
+      </c>
+      <c r="L6" t="n">
+        <v>506915</v>
+      </c>
+      <c r="M6" t="n">
+        <v>312642</v>
+      </c>
+      <c r="N6" t="n">
+        <v>819549</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6819994.278031</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>118632410</v>
+      </c>
+      <c r="R6" t="n">
+        <v>21893175</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2417199</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2417199</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="W6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4557707</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11500373</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-513425</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>513425</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>506915</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>312642</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>819549</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>22401912</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>117839238</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>49209023</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>51121346</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>48927268</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2194078</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1802808</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1638063</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>164745</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>140241150</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>793172</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>141034322</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>141034322</v>
       </c>
     </row>
   </sheetData>
@@ -1302,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW5"/>
+  <dimension ref="A1:BW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,876 +1738,965 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2417199</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2417199</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5802235</v>
-      </c>
-      <c r="E2" t="n">
-        <v>97027157</v>
-      </c>
-      <c r="F2" t="n">
-        <v>234958534</v>
-      </c>
-      <c r="G2" t="n">
-        <v>64820813</v>
-      </c>
-      <c r="H2" t="n">
-        <v>97027157</v>
-      </c>
-      <c r="I2" t="n">
-        <v>762235</v>
-      </c>
-      <c r="J2" t="n">
-        <v>229918534</v>
-      </c>
-      <c r="K2" t="n">
-        <v>233698534</v>
-      </c>
-      <c r="L2" t="n">
-        <v>229918534</v>
-      </c>
-      <c r="M2" t="n">
-        <v>229918534</v>
-      </c>
-      <c r="N2" t="n">
-        <v>26473547</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6899150</v>
-      </c>
-      <c r="P2" t="n">
-        <v>18232710</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>241720</v>
-      </c>
-      <c r="R2" t="n">
-        <v>241720</v>
-      </c>
-      <c r="S2" t="n">
-        <v>32384083</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4553100</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>26118</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4526983</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>746983</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3780000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>27830983</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8450134</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1275252</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>15252</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2494149</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>391009</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3721932</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>21836</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2395157</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1304939</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>262302617</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>169650820</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>84344</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8472130</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>921213</v>
-      </c>
+        <v>635711</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>10390</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>257629</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>921213</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4878419</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4878419</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>132891377</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>132891377</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>22403337</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-11542905</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>33946242</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>89565</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3614638</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5636988</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>24605051</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>92651796</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>994226</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>54149</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>54149</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>140524</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1951062</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>19079716</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="n">
+        <v>42938</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>234280</v>
+      </c>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="n">
-        <v>-11592</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>19091308</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>70432119</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>4979917</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>65452202</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>12516394</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>52935808</v>
-      </c>
+        <v>-69824</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2417199</v>
+        <v>2380144</v>
       </c>
       <c r="C3" t="n">
-        <v>2417199</v>
+        <v>2380144</v>
       </c>
       <c r="D3" t="n">
-        <v>7169215</v>
+        <v>8431130</v>
       </c>
       <c r="E3" t="n">
-        <v>67528498</v>
+        <v>120341140</v>
       </c>
       <c r="F3" t="n">
-        <v>233470033</v>
+        <v>232208680</v>
       </c>
       <c r="G3" t="n">
-        <v>42230886</v>
+        <v>91453989</v>
       </c>
       <c r="H3" t="n">
-        <v>67528498</v>
+        <v>120341140</v>
       </c>
       <c r="I3" t="n">
-        <v>764215</v>
+        <v>766130</v>
       </c>
       <c r="J3" t="n">
-        <v>227065033</v>
+        <v>224543680</v>
       </c>
       <c r="K3" t="n">
-        <v>232210033</v>
+        <v>230948680</v>
       </c>
       <c r="L3" t="n">
-        <v>227065033</v>
+        <v>224543680</v>
       </c>
       <c r="M3" t="n">
-        <v>227065033</v>
+        <v>224543680</v>
       </c>
       <c r="N3" t="n">
-        <v>36229989</v>
+        <v>38047889</v>
       </c>
       <c r="O3" t="n">
-        <v>317524</v>
+        <v>22681731</v>
       </c>
       <c r="P3" t="n">
-        <v>18232710</v>
+        <v>14422772</v>
       </c>
       <c r="Q3" t="n">
-        <v>241720</v>
+        <v>238014</v>
       </c>
       <c r="R3" t="n">
-        <v>241720</v>
+        <v>238014</v>
       </c>
       <c r="S3" t="n">
-        <v>31263115</v>
+        <v>19653761</v>
       </c>
       <c r="T3" t="n">
-        <v>6558820</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+        <v>9457456</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1643624</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1643624</v>
+      </c>
       <c r="W3" t="n">
-        <v>29148</v>
+        <v>22245</v>
       </c>
       <c r="X3" t="n">
-        <v>635710</v>
+        <v>635711</v>
       </c>
       <c r="Y3" t="n">
-        <v>5893962</v>
+        <v>7155876</v>
       </c>
       <c r="Z3" t="n">
-        <v>748962</v>
+        <v>750876</v>
       </c>
       <c r="AA3" t="n">
-        <v>5145000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>6405000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>22245</v>
+      </c>
       <c r="AC3" t="n">
-        <v>24704295</v>
+        <v>10196305</v>
       </c>
       <c r="AD3" t="n">
-        <v>4735282</v>
+        <v>4098465</v>
       </c>
       <c r="AE3" t="n">
-        <v>1275253</v>
+        <v>1275254</v>
       </c>
       <c r="AF3" t="n">
-        <v>15253</v>
+        <v>15254</v>
       </c>
       <c r="AG3" t="n">
         <v>1260000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2462361</v>
+        <v>841767</v>
       </c>
       <c r="AI3" t="n">
-        <v>98804</v>
+        <v>64461</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2370370</v>
+        <v>2566644</v>
       </c>
       <c r="AK3" t="n">
-        <v>17556</v>
+        <v>27845</v>
       </c>
       <c r="AL3" t="n">
-        <v>1238923</v>
+        <v>1988841</v>
       </c>
       <c r="AM3" t="n">
-        <v>1113891</v>
+        <v>549958</v>
       </c>
       <c r="AN3" t="n">
-        <v>258328148</v>
+        <v>244197441</v>
       </c>
       <c r="AO3" t="n">
-        <v>191392967</v>
+        <v>142547147</v>
       </c>
       <c r="AP3" t="n">
-        <v>84686</v>
+        <v>166170</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2039472</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>517619</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>638839</v>
+      </c>
       <c r="AS3" t="n">
-        <v>1903202</v>
+        <v>8790362</v>
       </c>
       <c r="AT3" t="n">
-        <v>1903202</v>
+        <v>8790362</v>
       </c>
       <c r="AU3" t="n">
-        <v>1903202</v>
+        <v>8790362</v>
       </c>
       <c r="AV3" t="n">
-        <v>3626510</v>
+        <v>3975734</v>
       </c>
       <c r="AW3" t="n">
-        <v>3626510</v>
+        <v>3975734</v>
       </c>
       <c r="AX3" t="n">
-        <v>159536535</v>
+        <v>104202540</v>
       </c>
       <c r="AY3" t="n">
-        <v>159536535</v>
+        <v>104202540</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24202562</v>
+        <v>24894722</v>
       </c>
       <c r="BA3" t="n">
-        <v>-10978932</v>
+        <v>-8160794</v>
       </c>
       <c r="BB3" t="n">
-        <v>35181494</v>
+        <v>33055516</v>
       </c>
       <c r="BC3" t="n">
-        <v>56466</v>
+        <v>130952</v>
       </c>
       <c r="BD3" t="n">
-        <v>3617187</v>
+        <v>3508541</v>
       </c>
       <c r="BE3" t="n">
-        <v>7007899</v>
+        <v>5021120</v>
       </c>
       <c r="BF3" t="n">
-        <v>24499942</v>
+        <v>24394903</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>66935181</v>
+        <v>101650294</v>
       </c>
       <c r="BI3" t="n">
-        <v>939840</v>
+        <v>1787640</v>
       </c>
       <c r="BJ3" t="n">
-        <v>61388</v>
+        <v>125673</v>
       </c>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>636453</v>
+        <v>1384486</v>
       </c>
       <c r="BO3" t="n">
-        <v>2670732</v>
+        <v>4874279</v>
       </c>
       <c r="BP3" t="n">
-        <v>8850840</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>-6564</v>
-      </c>
+        <v>7503110</v>
+      </c>
+      <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="n">
-        <v>8857404</v>
+        <v>7503110</v>
       </c>
       <c r="BS3" t="n">
-        <v>53835806</v>
+        <v>86100779</v>
       </c>
       <c r="BT3" t="n">
-        <v>16279832</v>
+        <v>55514788</v>
       </c>
       <c r="BU3" t="n">
-        <v>37555974</v>
+        <v>30585991</v>
       </c>
       <c r="BV3" t="n">
-        <v>11791076</v>
+        <v>16602700</v>
       </c>
       <c r="BW3" t="n">
-        <v>25764898</v>
+        <v>13983291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>2380144</v>
+        <v>2417199</v>
       </c>
       <c r="C4" t="n">
-        <v>2380144</v>
+        <v>2417199</v>
       </c>
       <c r="D4" t="n">
-        <v>8431130</v>
+        <v>7169215</v>
       </c>
       <c r="E4" t="n">
-        <v>120341140</v>
+        <v>67528498</v>
       </c>
       <c r="F4" t="n">
-        <v>232208680</v>
+        <v>233470033</v>
       </c>
       <c r="G4" t="n">
-        <v>91453989</v>
+        <v>42230886</v>
       </c>
       <c r="H4" t="n">
-        <v>120341140</v>
+        <v>67528498</v>
       </c>
       <c r="I4" t="n">
-        <v>766130</v>
+        <v>764215</v>
       </c>
       <c r="J4" t="n">
-        <v>224543680</v>
+        <v>227065033</v>
       </c>
       <c r="K4" t="n">
-        <v>230948680</v>
+        <v>232210033</v>
       </c>
       <c r="L4" t="n">
-        <v>224543680</v>
+        <v>227065033</v>
       </c>
       <c r="M4" t="n">
-        <v>224543680</v>
+        <v>227065033</v>
       </c>
       <c r="N4" t="n">
-        <v>38047889</v>
+        <v>36229989</v>
       </c>
       <c r="O4" t="n">
-        <v>22681731</v>
+        <v>317524</v>
       </c>
       <c r="P4" t="n">
-        <v>14422772</v>
+        <v>18232710</v>
       </c>
       <c r="Q4" t="n">
-        <v>238014</v>
+        <v>241720</v>
       </c>
       <c r="R4" t="n">
-        <v>238014</v>
+        <v>241720</v>
       </c>
       <c r="S4" t="n">
-        <v>19653761</v>
+        <v>31263115</v>
       </c>
       <c r="T4" t="n">
-        <v>9457456</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1643624</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1643624</v>
-      </c>
+        <v>6558820</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>22245</v>
+        <v>29148</v>
       </c>
       <c r="X4" t="n">
-        <v>635711</v>
+        <v>635710</v>
       </c>
       <c r="Y4" t="n">
-        <v>7155876</v>
+        <v>5893962</v>
       </c>
       <c r="Z4" t="n">
-        <v>750876</v>
+        <v>748962</v>
       </c>
       <c r="AA4" t="n">
-        <v>6405000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>22245</v>
-      </c>
+        <v>5145000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>10196305</v>
+        <v>24704295</v>
       </c>
       <c r="AD4" t="n">
-        <v>4098465</v>
+        <v>4735282</v>
       </c>
       <c r="AE4" t="n">
-        <v>1275254</v>
+        <v>1275253</v>
       </c>
       <c r="AF4" t="n">
-        <v>15254</v>
+        <v>15253</v>
       </c>
       <c r="AG4" t="n">
         <v>1260000</v>
       </c>
       <c r="AH4" t="n">
-        <v>841767</v>
+        <v>2462361</v>
       </c>
       <c r="AI4" t="n">
-        <v>64461</v>
+        <v>98804</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2566644</v>
+        <v>2370370</v>
       </c>
       <c r="AK4" t="n">
-        <v>27845</v>
+        <v>17556</v>
       </c>
       <c r="AL4" t="n">
-        <v>1988841</v>
+        <v>1238923</v>
       </c>
       <c r="AM4" t="n">
-        <v>549958</v>
+        <v>1113891</v>
       </c>
       <c r="AN4" t="n">
-        <v>244197441</v>
+        <v>258328148</v>
       </c>
       <c r="AO4" t="n">
-        <v>142547147</v>
+        <v>191392967</v>
       </c>
       <c r="AP4" t="n">
-        <v>166170</v>
+        <v>84686</v>
       </c>
       <c r="AQ4" t="n">
-        <v>517619</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>638839</v>
-      </c>
+        <v>2039472</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>8790362</v>
+        <v>1903202</v>
       </c>
       <c r="AT4" t="n">
-        <v>8790362</v>
+        <v>1903202</v>
       </c>
       <c r="AU4" t="n">
-        <v>8790362</v>
+        <v>1903202</v>
       </c>
       <c r="AV4" t="n">
-        <v>3975734</v>
+        <v>3626510</v>
       </c>
       <c r="AW4" t="n">
-        <v>3975734</v>
+        <v>3626510</v>
       </c>
       <c r="AX4" t="n">
-        <v>104202540</v>
+        <v>159536535</v>
       </c>
       <c r="AY4" t="n">
-        <v>104202540</v>
+        <v>159536535</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24894722</v>
+        <v>24202562</v>
       </c>
       <c r="BA4" t="n">
-        <v>-8160794</v>
+        <v>-10978932</v>
       </c>
       <c r="BB4" t="n">
-        <v>33055516</v>
+        <v>35181494</v>
       </c>
       <c r="BC4" t="n">
-        <v>130952</v>
+        <v>56466</v>
       </c>
       <c r="BD4" t="n">
-        <v>3508541</v>
+        <v>3617187</v>
       </c>
       <c r="BE4" t="n">
-        <v>5021120</v>
+        <v>7007899</v>
       </c>
       <c r="BF4" t="n">
-        <v>24394903</v>
+        <v>24499942</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>101650294</v>
+        <v>66935181</v>
       </c>
       <c r="BI4" t="n">
-        <v>1787640</v>
+        <v>939840</v>
       </c>
       <c r="BJ4" t="n">
-        <v>125673</v>
+        <v>61388</v>
       </c>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="BN4" t="n">
-        <v>1384486</v>
+        <v>636453</v>
       </c>
       <c r="BO4" t="n">
-        <v>4874279</v>
+        <v>2670732</v>
       </c>
       <c r="BP4" t="n">
-        <v>7503110</v>
-      </c>
-      <c r="BQ4" t="inlineStr"/>
+        <v>8850840</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-6564</v>
+      </c>
       <c r="BR4" t="n">
-        <v>7503110</v>
+        <v>8857404</v>
       </c>
       <c r="BS4" t="n">
-        <v>86100779</v>
+        <v>53835806</v>
       </c>
       <c r="BT4" t="n">
-        <v>55514788</v>
+        <v>16279832</v>
       </c>
       <c r="BU4" t="n">
-        <v>30585991</v>
+        <v>37555974</v>
       </c>
       <c r="BV4" t="n">
-        <v>16602700</v>
+        <v>11791076</v>
       </c>
       <c r="BW4" t="n">
-        <v>13983291</v>
+        <v>25764898</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2366921</v>
+        <v>2417199</v>
       </c>
       <c r="C5" t="n">
-        <v>2366921</v>
+        <v>2417199</v>
       </c>
       <c r="D5" t="n">
-        <v>9589979</v>
+        <v>5802235</v>
       </c>
       <c r="E5" t="n">
-        <v>133918294</v>
+        <v>97027157</v>
       </c>
       <c r="F5" t="n">
-        <v>206157291</v>
+        <v>234958534</v>
       </c>
       <c r="G5" t="n">
-        <v>115618963</v>
+        <v>64820813</v>
       </c>
       <c r="H5" t="n">
-        <v>133918294</v>
+        <v>97027157</v>
       </c>
       <c r="I5" t="n">
-        <v>769979</v>
+        <v>762235</v>
       </c>
       <c r="J5" t="n">
-        <v>197337291</v>
+        <v>229918534</v>
       </c>
       <c r="K5" t="n">
-        <v>204897291</v>
+        <v>233698534</v>
       </c>
       <c r="L5" t="n">
-        <v>197337291</v>
+        <v>229918534</v>
       </c>
       <c r="M5" t="n">
-        <v>197337291</v>
+        <v>229918534</v>
       </c>
       <c r="N5" t="n">
-        <v>35092206</v>
+        <v>26473547</v>
       </c>
       <c r="O5" t="n">
-        <v>28477497</v>
+        <v>6899150</v>
       </c>
       <c r="P5" t="n">
-        <v>13063204</v>
+        <v>18232710</v>
       </c>
       <c r="Q5" t="n">
-        <v>236692</v>
+        <v>241720</v>
       </c>
       <c r="R5" t="n">
-        <v>236692</v>
+        <v>241720</v>
       </c>
       <c r="S5" t="n">
-        <v>22175673</v>
+        <v>32384083</v>
       </c>
       <c r="T5" t="n">
-        <v>8961346</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+        <v>4553100</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>26118</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
-        <v>10390</v>
-      </c>
-      <c r="X5" t="n">
-        <v>635711</v>
-      </c>
       <c r="Y5" t="n">
-        <v>8315245</v>
+        <v>4526983</v>
       </c>
       <c r="Z5" t="n">
-        <v>755245</v>
+        <v>746983</v>
       </c>
       <c r="AA5" t="n">
-        <v>7560000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>10390</v>
-      </c>
+        <v>3780000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>13214327</v>
+        <v>27830983</v>
       </c>
       <c r="AD5" t="n">
-        <v>5060186</v>
+        <v>8450134</v>
       </c>
       <c r="AE5" t="n">
-        <v>1274734</v>
+        <v>1275252</v>
       </c>
       <c r="AF5" t="n">
-        <v>14734</v>
+        <v>15252</v>
       </c>
       <c r="AG5" t="n">
         <v>1260000</v>
       </c>
       <c r="AH5" t="n">
-        <v>651032</v>
+        <v>2494149</v>
       </c>
       <c r="AI5" t="n">
-        <v>661422</v>
+        <v>391009</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2059296</v>
+        <v>3721932</v>
       </c>
       <c r="AK5" t="n">
-        <v>11417</v>
+        <v>5300</v>
       </c>
       <c r="AL5" t="n">
-        <v>744927</v>
+        <v>2395157</v>
       </c>
       <c r="AM5" t="n">
-        <v>1302952</v>
+        <v>1321475</v>
       </c>
       <c r="AN5" t="n">
-        <v>219512964</v>
+        <v>262302617</v>
       </c>
       <c r="AO5" t="n">
-        <v>90679674</v>
+        <v>169650820</v>
       </c>
       <c r="AP5" t="n">
-        <v>99083</v>
+        <v>84344</v>
       </c>
       <c r="AQ5" t="n">
-        <v>957488</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>257629</v>
-      </c>
+        <v>8472130</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>921213</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>178448</v>
+      </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>742765</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>4878419</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>4878419</v>
       </c>
       <c r="AX5" t="n">
-        <v>63418997</v>
+        <v>132891377</v>
       </c>
       <c r="AY5" t="n">
-        <v>63418997</v>
+        <v>132891377</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25946477</v>
+        <v>22403337</v>
       </c>
       <c r="BA5" t="n">
-        <v>-5460700</v>
+        <v>-11542905</v>
       </c>
       <c r="BB5" t="n">
-        <v>31407177</v>
+        <v>33946242</v>
       </c>
       <c r="BC5" t="n">
-        <v>374314</v>
+        <v>89565</v>
       </c>
       <c r="BD5" t="n">
-        <v>3459479</v>
+        <v>3614638</v>
       </c>
       <c r="BE5" t="n">
-        <v>3267414</v>
+        <v>5636988</v>
       </c>
       <c r="BF5" t="n">
-        <v>24305970</v>
+        <v>24605051</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>128833290</v>
+        <v>92651796</v>
       </c>
       <c r="BI5" t="n">
-        <v>752342</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>42938</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>234280</v>
-      </c>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
+        <v>994226</v>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
+        <v>54149</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>54149</v>
+      </c>
       <c r="BN5" t="n">
-        <v>334385</v>
+        <v>140524</v>
       </c>
       <c r="BO5" t="n">
-        <v>5821530</v>
+        <v>1951062</v>
       </c>
       <c r="BP5" t="n">
-        <v>14657593</v>
+        <v>19079716</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-69824</v>
+        <v>-11592</v>
       </c>
       <c r="BR5" t="n">
-        <v>14657593</v>
+        <v>19091308</v>
       </c>
       <c r="BS5" t="n">
-        <v>107267440</v>
+        <v>70432119</v>
       </c>
       <c r="BT5" t="n">
-        <v>80518910</v>
+        <v>4979917</v>
       </c>
       <c r="BU5" t="n">
-        <v>26748530</v>
+        <v>65452202</v>
       </c>
       <c r="BV5" t="n">
+        <v>12516394</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>52935808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2417199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2417199</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4540187</v>
+      </c>
+      <c r="E6" t="n">
+        <v>114690670</v>
+      </c>
+      <c r="F6" t="n">
+        <v>240201687</v>
+      </c>
+      <c r="G6" t="n">
+        <v>63682285</v>
+      </c>
+      <c r="H6" t="n">
+        <v>114690670</v>
+      </c>
+      <c r="I6" t="n">
+        <v>760187</v>
+      </c>
+      <c r="J6" t="n">
+        <v>236421687</v>
+      </c>
+      <c r="K6" t="n">
+        <v>238941687</v>
+      </c>
+      <c r="L6" t="n">
+        <v>236421687</v>
+      </c>
+      <c r="M6" t="n">
+        <v>236421687</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26034034</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6952666</v>
+      </c>
+      <c r="P6" t="n">
+        <v>18232710</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>241720</v>
+      </c>
+      <c r="R6" t="n">
+        <v>241720</v>
+      </c>
+      <c r="S6" t="n">
+        <v>32382877</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3291493</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>26558</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>3264935</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>744935</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2520000</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>29091384</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10194173</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1275252</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>15252</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>923200</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>294795</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5885062</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>4350</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3271778</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2608934</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>268804564</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>176030895</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>439059</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6947323</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>24136239</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>37942</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>24098297</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1406140</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1406140</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>121731017</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>121731017</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>21371117</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-13624938</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>34996055</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>307571</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3665988</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6375145</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>24647351</v>
+      </c>
+      <c r="BG6" t="n">
         <v>0</v>
       </c>
-      <c r="BW5" t="n">
-        <v>26748530</v>
+      <c r="BH6" t="n">
+        <v>92773669</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1116342</v>
+      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>43974</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>43974</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>169697</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1901333</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>17835284</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-20825</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>17856109</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>71707039</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>26498046</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>45208993</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>21694427</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>23514566</v>
       </c>
     </row>
   </sheetData>
@@ -2562,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO5"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,481 +2914,548 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Other Cash Adjustment Outside Changein Cash</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1491422</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-8631044</v>
-      </c>
-      <c r="E2" t="n">
-        <v>65452202</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37555974</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1834080</v>
-      </c>
-      <c r="H2" t="n">
-        <v>29730308</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1788736</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-423736</v>
-      </c>
+        <v>656209</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>656209</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-1365000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1365000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>21396578</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1262088</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1016530</v>
-      </c>
-      <c r="R2" t="n">
-        <v>27219056</v>
-      </c>
-      <c r="S2" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-4780944</v>
-      </c>
+        <v>656209</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>-8631044</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-8631044</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>10122466</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-750669</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-8261501</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-2407131</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>6911676</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-52639</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-12742165</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>490672</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-4123283</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>19813340</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>18617529</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1195811</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-4045649</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>983894</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1834080</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>6889150</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>-28878349</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-36914749</v>
+        <v>-12747971</v>
       </c>
       <c r="C3" t="n">
-        <v>3830746</v>
+        <v>1366994</v>
       </c>
       <c r="D3" t="n">
-        <v>-58813599</v>
+        <v>-45679530</v>
       </c>
       <c r="E3" t="n">
-        <v>37555974</v>
+        <v>30585991</v>
       </c>
       <c r="F3" t="n">
-        <v>30585991</v>
+        <v>26748530</v>
       </c>
       <c r="G3" t="n">
-        <v>-1050114</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8020097</v>
+        <v>3837461</v>
       </c>
       <c r="I3" t="n">
-        <v>2328105</v>
+        <v>-252635</v>
       </c>
       <c r="J3" t="n">
-        <v>-242641</v>
+        <v>-464629</v>
       </c>
       <c r="K3" t="n">
-        <v>3830746</v>
+        <v>1366994</v>
       </c>
       <c r="L3" t="n">
-        <v>3830746</v>
+        <v>1366994</v>
       </c>
       <c r="M3" t="n">
-        <v>-1260000</v>
+        <v>-1155000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1260000</v>
+        <v>-1155000</v>
       </c>
       <c r="O3" t="n">
-        <v>-16206858</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-43000000</v>
-      </c>
+        <v>-28841463</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>3293710</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>81630632</v>
+        <v>20572422</v>
       </c>
       <c r="S3" t="n">
-        <v>141382744</v>
+        <v>188888911</v>
       </c>
       <c r="T3" t="n">
-        <v>-59752112</v>
+        <v>-168316489</v>
       </c>
       <c r="U3" t="n">
+        <v>-2619216</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-2619216</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-45679530</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-45679530</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-45679530</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>32931559</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1161964</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2900472</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-3910865</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-404648</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AF3" t="n">
+        <v>7013396</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-3261716</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>4336525</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5891465</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5035631</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>855834</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2955683</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-1618722</v>
+      </c>
+      <c r="AN3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>-58813599</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-58813599</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
-        <v>21898850</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>751444</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>13481015</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13155781</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-806684</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-1510</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-494069</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-2565926</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-820200</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>4171765</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2858174</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1313591</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-1817900</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>6951661</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1050114</v>
-      </c>
       <c r="AO3" t="n">
-        <v>525609</v>
-      </c>
+        <v>22889816</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-12747971</v>
+        <v>-36914749</v>
       </c>
       <c r="C4" t="n">
-        <v>1366994</v>
+        <v>3830746</v>
       </c>
       <c r="D4" t="n">
-        <v>-45679530</v>
+        <v>-58813599</v>
       </c>
       <c r="E4" t="n">
+        <v>37555974</v>
+      </c>
+      <c r="F4" t="n">
         <v>30585991</v>
       </c>
-      <c r="F4" t="n">
-        <v>26748530</v>
-      </c>
       <c r="G4" t="n">
+        <v>-1050114</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8020097</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2328105</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-242641</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3830746</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3830746</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-1260000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1260000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-16206858</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-43000000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3293710</v>
+      </c>
+      <c r="R4" t="n">
+        <v>81630632</v>
+      </c>
+      <c r="S4" t="n">
+        <v>141382744</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-59752112</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
-        <v>3837461</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-252635</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-464629</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1366994</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1366994</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-1155000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-1155000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-28841463</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>20572422</v>
-      </c>
-      <c r="S4" t="n">
-        <v>188888911</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-168316489</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-2619216</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-2619216</v>
-      </c>
       <c r="W4" t="n">
-        <v>-45679530</v>
+        <v>-58813599</v>
       </c>
       <c r="X4" t="n">
-        <v>-45679530</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-45679530</v>
-      </c>
+        <v>-58813599</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>32931559</v>
+        <v>21898850</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1161964</v>
+        <v>751444</v>
       </c>
       <c r="AB4" t="n">
-        <v>2900472</v>
+        <v>13481015</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3910865</v>
+        <v>13155781</v>
       </c>
       <c r="AD4" t="n">
-        <v>-404648</v>
+        <v>-806684</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-1510</v>
       </c>
       <c r="AF4" t="n">
-        <v>7013396</v>
+        <v>-494069</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3261716</v>
+        <v>-2565926</v>
       </c>
       <c r="AH4" t="n">
-        <v>4336525</v>
+        <v>-820200</v>
       </c>
       <c r="AI4" t="n">
-        <v>5891465</v>
+        <v>4171765</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5035631</v>
+        <v>2858174</v>
       </c>
       <c r="AK4" t="n">
-        <v>855834</v>
+        <v>1313591</v>
       </c>
       <c r="AL4" t="n">
-        <v>2955683</v>
+        <v>-1817900</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1618722</v>
+        <v>6951661</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1050114</v>
       </c>
       <c r="AO4" t="n">
-        <v>22889816</v>
-      </c>
+        <v>525609</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>12063940</v>
+        <v>-48009675</v>
       </c>
       <c r="C5" t="n">
-        <v>656209</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-28878349</v>
+        <v>-58132141</v>
       </c>
       <c r="E5" t="n">
-        <v>26748530</v>
+        <v>65452202</v>
       </c>
       <c r="F5" t="n">
-        <v>24134648</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>37555974</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1834080</v>
+      </c>
       <c r="H5" t="n">
-        <v>2613882</v>
+        <v>-37032877</v>
       </c>
       <c r="I5" t="n">
-        <v>-927524</v>
+        <v>-1788736</v>
       </c>
       <c r="J5" t="n">
-        <v>-323733</v>
+        <v>-423736</v>
       </c>
       <c r="K5" t="n">
-        <v>656209</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>656209</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1260000</v>
+        <v>-1365000</v>
       </c>
       <c r="N5" t="n">
-        <v>-1260000</v>
+        <v>-1365000</v>
       </c>
       <c r="O5" t="n">
-        <v>-37400883</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>-45366607</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1262088</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1016530</v>
+      </c>
       <c r="R5" t="n">
-        <v>-10397591</v>
+        <v>11219056</v>
       </c>
       <c r="S5" t="n">
-        <v>111844368</v>
+        <v>16000000</v>
       </c>
       <c r="T5" t="n">
-        <v>-122241959</v>
+        <v>-4780944</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-28878349</v>
+        <v>-58132141</v>
       </c>
       <c r="X5" t="n">
-        <v>-28878349</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-28878349</v>
-      </c>
+        <v>-58132141</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>40942289</v>
+        <v>10122466</v>
       </c>
       <c r="AA5" t="n">
-        <v>1028187</v>
+        <v>-750669</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2925844</v>
+        <v>-8261489</v>
       </c>
       <c r="AC5" t="n">
-        <v>3736945</v>
+        <v>-2407131</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1779148</v>
+        <v>6911676</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-52639</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4883641</v>
+        <v>-12742153</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1261998</v>
+        <v>490672</v>
       </c>
       <c r="AH5" t="n">
-        <v>3148882</v>
+        <v>-4123283</v>
       </c>
       <c r="AI5" t="n">
-        <v>8920103</v>
+        <v>19813340</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8106242</v>
+        <v>18617529</v>
       </c>
       <c r="AK5" t="n">
-        <v>8920103</v>
+        <v>1195811</v>
       </c>
       <c r="AL5" t="n">
-        <v>3347377</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>-4045649</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>983894</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1834080</v>
+      </c>
       <c r="AO5" t="n">
-        <v>28585582</v>
+        <v>6899150</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>66763185</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>26129414</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>-37993692</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45208993</v>
+      </c>
+      <c r="F6" t="n">
+        <v>65452202</v>
+      </c>
+      <c r="G6" t="n">
+        <v>839255</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-19485277</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1538848</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-278848</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>-1260000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1260000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-82069535</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>884456</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-44990047</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4609847</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-49599894</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>-37993692</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-37993692</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>64123106</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>65197</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>35331</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1543142</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2148066</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>10182</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>990735</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-1002838</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4557707</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>50224225</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>48927268</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1296957</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-439513</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-245374</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>513425</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1597187</v>
       </c>
     </row>
   </sheetData>
@@ -3254,7 +3469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS2"/>
+  <dimension ref="A1:DT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3410,465 +3625,470 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>trailingPE</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3968,356 +4188,359 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>34</v>
+        <v>34.14</v>
       </c>
       <c r="V2" t="n">
-        <v>34</v>
+        <v>33.54</v>
       </c>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>33.54</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>33.54</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>34.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>33.54</v>
       </c>
       <c r="AA2" t="n">
-        <v>34</v>
+        <v>33.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>34</v>
+        <v>33.54</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.024</v>
+        <v>-0.045</v>
       </c>
       <c r="AE2" t="n">
-        <v>755</v>
+        <v>32.56311</v>
       </c>
       <c r="AF2" t="n">
         <v>755</v>
       </c>
       <c r="AG2" t="n">
-        <v>42</v>
+        <v>755</v>
       </c>
       <c r="AH2" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>33.28</v>
       </c>
       <c r="AL2" t="n">
-        <v>82184768</v>
+        <v>34.78</v>
       </c>
       <c r="AM2" t="n">
-        <v>85521970</v>
+        <v>81072856</v>
       </c>
       <c r="AN2" t="n">
+        <v>83782375</v>
+      </c>
+      <c r="AO2" t="n">
         <v>29.16</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>56.65</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>165.6</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>29.16</v>
       </c>
-      <c r="AR2" t="n">
-        <v>33.6548</v>
-      </c>
       <c r="AS2" t="n">
-        <v>36.2694</v>
+        <v>34.0444</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>36.0517</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="AW2" t="b">
+      <c r="AX2" t="b">
         <v>0</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>0.04923</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AZ2" t="n">
         <v>2014107</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>2417199</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>0.06987</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>0.12342</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>2417199</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>104.025</v>
       </c>
-      <c r="BE2" t="n">
-        <v>0.3268445</v>
-      </c>
       <c r="BF2" t="n">
+        <v>0.3224225</v>
+      </c>
+      <c r="BG2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BI2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BI2" t="n">
-        <v>-1.83</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>-0.30498773</v>
+        <v>1.03</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BL2" t="inlineStr">
+        <v>-0.34219652</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.22635591</v>
+      </c>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BM2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN2" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>23710604</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>3.147</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BR2" t="n">
         <v>3.189</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="BS2" t="n">
         <v>1.92</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="BT2" t="n">
         <v>0.05269</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="BU2" t="n">
         <v>0.029779999</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="BV2" t="n">
         <v>27888520</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="BW2" t="n">
         <v>0.172</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="BX2" t="n">
         <v>0.8748</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="BY2" t="n">
         <v>0.16812</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="BZ2" t="n">
         <v>0</v>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>PLN</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>11C.F</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CF2" t="b">
+      <c r="CG2" t="b">
         <v>0</v>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1582095600000</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.5999985</v>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>33.54 - 33.54</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="CO2" t="n">
+        <v>41</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>4.380001</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.1502058</v>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>29.16 - 56.65</t>
+        </is>
+      </c>
+      <c r="CS2" t="n">
+        <v>-23.11</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>-0.40794352</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>-34.219654</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1755687540</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1756123200</v>
+      </c>
+      <c r="CX2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.50439835</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.014815898</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-2.5116997</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.06966938</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>11 bit studios SA             I</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>11 bit studios S.A.</t>
         </is>
       </c>
-      <c r="CJ2" t="n">
-        <v>1780380267</v>
-      </c>
-      <c r="CK2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>-1.7574648</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>1780985164</v>
+      </c>
+      <c r="DM2" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>finmb_114978149</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>Europe/Berlin</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="CO2" t="n">
+      <c r="DQ2" t="n">
         <v>7200000</v>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>dr_market</t>
         </is>
       </c>
-      <c r="CQ2" t="b">
+      <c r="DS2" t="b">
         <v>0</v>
       </c>
-      <c r="CR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>34</v>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>1582095600000</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>34.0 - 34.0</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="CZ2" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.1659808</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>29.16 - 56.65</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
-        <v>-22.650002</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.3998235</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-30.498774</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>1755687540</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1756123200</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.34519958</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.010257068</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-2.2694016</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.06257069</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
